--- a/data/proofserve/output/internal_linking_report.xlsx
+++ b/data/proofserve/output/internal_linking_report.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-servers</t>
+          <t>https://www.proofserve.com/for-partners</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -474,13 +474,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/become-a-process-server</t>
+          <t>https://www.proofserve.com/landing-page/proof-vs-abc-legal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -513,7 +513,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/how-it-works</t>
+          <t>https://www.proofserve.com/for-government</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/</t>
+          <t>https://www.proofserve.com/for-individuals</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="D5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/pricing</t>
+          <t>https://www.proofserve.com/for-process-serving-companies</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2613</v>
+        <v>1</v>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -585,22 +585,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/about</t>
+          <t>https://www.proofserve.com/skip-tracing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -609,22 +609,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-partners</t>
+          <t>https://www.proofserve.com/for-law-enforcement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -633,22 +633,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/pro-se-terms-of-service</t>
+          <t>https://www.proofserve.com/for-collections-agencies</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -657,22 +657,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-government</t>
+          <t>https://www.proofserve.com/for-servers</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -681,22 +681,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-individuals</t>
+          <t>https://www.proofserve.com/for-law-firms</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -705,22 +705,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-process-serving-companies</t>
+          <t>https://www.proofserve.com/become-a-process-server</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -729,46 +729,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/get-quote</t>
+          <t>https://www.proofserve.com/how-it-works</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/our-commitment-to-integrity</t>
+          <t>https://www.proofserve.com/pricing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2613</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/skip-tracing</t>
+          <t>https://www.proofserve.com/about</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-law-enforcement</t>
+          <t>https://www.proofserve.com/calculator/collection</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -825,7 +825,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-collections-agencies</t>
+          <t>https://www.proofserve.com/calculator/firm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
         <v>3</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -849,7 +849,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-law-firms</t>
+          <t>https://www.proofserve.com/calculator/property-management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -858,15 +858,159 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/serve-center</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/get-quote</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/request-a-demo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/contact</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/property-management</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,7 +1053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/become-a-process-server</t>
+          <t>https://www.proofserve.com/for-law-firms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -919,211 +1063,3031 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-law-firms</t>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-to-find-the-right-process-server</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7269999980926514</v>
+        <v>0.7789999842643738</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/our-commitment-to-integrity</t>
+          <t>https://www.proofserve.com/for-law-firms</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/_development/our-commitment-to-integrity</t>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7900000214576721</v>
+        <v>0.7720000147819519</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/about</t>
+          <t>https://www.proofserve.com/for-law-firms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-legal-tech-is-transforming-the-role-of-process-servers-and-service-of</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.765999972820282</v>
+        <v>0.7720000147819519</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-partners</t>
+          <t>https://www.proofserve.com/become-a-process-server</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/what-paralegals-should-look-for-when-working-with-a-process-server</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7630000114440918</v>
+        <v>0.7689999938011169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/about</t>
+          <t>https://www.proofserve.com/for-partners</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7580000162124634</v>
+        <v>0.7609999775886536</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/pro-se-terms-of-service</t>
+          <t>https://www.proofserve.com/for-law-firms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/legal/terms-of-service</t>
+          <t>https://www.proofserve.com/learn/proof-best-practices/how-litigation-law-firms-scale-service-of-process</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7559999823570251</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-law-firms</t>
+          <t>https://www.proofserve.com/for-partners</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/learn/paralegal-productivity/how-to-find-the-right-process-server</t>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7250000238418579</v>
+        <v>0.7490000128746033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-partners</t>
+          <t>https://www.proofserve.com/how-it-works</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
+          <t>https://www.proofserve.com/learn/proof-best-practices/how-litigation-law-firms-scale-service-of-process</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7220000028610229</v>
+        <v>0.7480000257492065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/for-partners</t>
+          <t>https://www.proofserve.com/how-it-works</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/associations</t>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-legal-tech-is-transforming-the-role-of-process-servers-and-service-of</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7200000286102295</v>
+        <v>0.7480000257492065</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/integrations/clio</t>
+          <t>https://www.proofserve.com/for-partners</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7459999918937683</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7429999709129333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7409999966621399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/what-paralegals-should-look-for-when-working-with-a-process-server</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7350000143051147</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-legal-tech-is-transforming-the-role-of-process-servers-and-service-of</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7319999933242798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-to-find-the-right-process-server</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7269999980926514</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.718999981880188</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/motion-to-dismiss</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.718999981880188</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/property-managers-streamline-service-of-process-with-process-server-provider</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7179999947547913</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/what-happens-if-you-can-t-serve-someone-court-papers</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.7139999866485596</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.7129999995231628</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/texas-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.7089999914169312</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-process-serving-companies</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/consenting-to-service-of-process</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7089999914169312</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/what-happens-when-a-court-blacklists-your-process-server</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7059999704360962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-process-serving-companies</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/process-server-life</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7059999704360962</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-servers</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/what-paralegals-should-look-for-when-working-with-a-process-server</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.703000009059906</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/california-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.699999988079071</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-servers</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/gate-codes-and-gated-access-what-every-process-server-needs-to-know</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.6990000009536743</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/risks-and-mitigation-strategies</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6970000267028809</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6959999799728394</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/how-litigation-law-firms-scale-service-of-process</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6949999928474426</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-process-serving-companies</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6940000057220459</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/property-managers-streamline-service-of-process-with-process-server-provider</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.6930000185966492</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/process-server-life</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/who-can-accept-served-papers</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/consenting-to-service-of-process</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6869999766349792</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.6869999766349792</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/what-skills-are-needed-to-be-a-successful-process-server</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.6850000023841858</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/30-years-of-legal-tech-innovation</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.6850000023841858</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/personal-service-vs-substituted-service</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6850000023841858</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/integrate-proof-with-your-litify</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6850000023841858</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/motion-to-dismiss</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6840000152587891</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/what-skills-are-needed-to-be-a-successful-process-server</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6840000152587891</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/new-york-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.6840000152587891</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/how-it-works</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6800000071525574</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/biggest-problems-with-process-serving</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.6769999861717224</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/california-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6769999861717224</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/how-it-works</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/consenting-to-service-of-process</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6759999990463257</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-government</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-to-find-the-right-process-server</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.6740000247955322</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/who-serves-court-papers</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6729999780654907</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-servers</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/process-server-life</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.6710000038146973</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-wins-clio-integration-award-for-best-practice-of-law-app</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/consenting-to-service-of-process</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.6679999828338623</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/a-new-era-of-process-serving-in-florida-the-impact-of-hb-837-on-the-legal</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.6669999957084656</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/biggest-problems-with-process-serving</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.6650000214576721</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.6639999747276306</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-partners</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/how-proof-helped-legal-teams-transform-service-of-process-in-2024</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.6639999747276306</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-process-serving-companies</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-to-find-the-right-process-server</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.6639999747276306</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.6629999876022339</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/avoiding-service-of-process</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.6629999876022339</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.6629999876022339</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/integrate-proof-with-your-litify</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.6620000004768372</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/who-serves-court-papers</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.6620000004768372</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/colorado-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.6620000004768372</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/the-truth-about-process-servers</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.6620000004768372</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/how-it-works</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/personal-service-vs-substituted-service</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.6610000133514404</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/how-it-works</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.6600000262260437</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/how-proof-helped-legal-teams-transform-service-of-process-in-2024</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.6589999794960022</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-government</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.6579999923706055</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/who-can-accept-served-papers</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.6570000052452087</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/landing-page/proof-vs-abc-legal</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.6570000052452087</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/how-litigation-law-firms-scale-service-of-process</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.656000018119812</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/florida-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.656000018119812</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-law-firms</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/how-to-serve-someone-who-is-avoiding-service</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.656000018119812</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/how-it-works</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/30-years-of-legal-tech-innovation</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.656000018119812</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/colorado-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.6549999713897705</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/avoiding-service-of-process</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.6549999713897705</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/biggest-problems-with-process-serving</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.6549999713897705</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/become-a-process-server</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/cook-county-ends-mandatory-sheriff-serves-what-law-firms-need-to-know-for-2025</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.6539999842643738</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-individuals</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/7-things-every-collections-professional-should-know-about-service-of-process</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.6529999971389771</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/how-it-works</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/process-server-best-practices/process-server-life</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.6529999971389771</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/for-process-serving-companies</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/how-to-serve-someone-who-is-avoiding-service</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.6510000228881836</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/landing-page/proof-vs-abc-legal</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.6510000228881836</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.7540000081062317</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.7360000014305115</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>https://www.proofserve.com/calculator/firm</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.7260000109672546</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-wins-clio-integration-award-for-best-practice-of-law-app</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.6959999799728394</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.6880000233650208</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/podcast-highlights-from-great-entrepreneurs-with-rj-lumba</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.6869999766349792</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/property-managers-streamline-service-of-process-with-process-server-provider</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.6850000023841858</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-legal-tech-is-transforming-the-role-of-process-servers-and-service-of</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.6830000281333923</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/consenting-to-service-of-process</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.6830000281333923</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.6819999814033508</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/calculator/firm</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/7-best-productivity-tips-for-paralegals</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.6809999942779541</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/calculator/firm</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/scaling-high-volume-service-of-process-key-takeaways-for-personal-injury-teams</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.6769999861717224</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/personal-service-vs-substituted-service</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.6690000295639038</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/product-updates/how-proof-built-60-second-serve-requests-with-ai</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.6679999828338623</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/8-ways-to-optimize-the-litigation-timeline</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.6669999957084656</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/serve-center</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-your-law-firms-service-of-process-filevine-integration-with-proof</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.6669999957084656</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/calculator/property-management</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/property-managers-streamline-service-of-process-with-process-server-provider</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.6570000052452087</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/california-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.6549999713897705</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/about</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/state-of-the-paralegal-market-whats-big-in-legal-tech-and-whats-next</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.6539999842643738</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/risks-and-mitigation-strategies</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.6529999971389771</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/service-of-process-guide</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/texas-service-of-process-rules</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.6510000228881836</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.8830000162124634</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio-cloud-conference-gift-card</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.8169999718666077</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/filevine</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/product-updates/streamline-your-serve-workflow-with-filevine-taskflows-and-deadline-chains</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.7749999761581421</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-wins-clio-integration-award-for-best-practice-of-law-app</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.7590000033378601</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.7400000095367432</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.7400000095367432</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-your-law-firms-service-of-process-filevine-integration-with-proof</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.7289999723434448</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-your-law-firms-service-of-process-filevine-integration-with-proof</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.7289999723434448</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/landing-page/webinar-event/how-to-scale-collections-in-serve-first-states</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/how-to-scale-collections-in-serve-first-states</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.7250000238418579</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/integrate-proof-with-your-litify</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.7170000076293945</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.7170000076293945</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.7170000076293945</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/cook-county-ends-mandatory-sheriff-serves-what-law-firms-need-to-know-for-2025</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.7089999914169312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/cook-county-ends-mandatory-sheriff-serves-what-law-firms-need-to-know-for-2025</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7089999914169312</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.6990000009536743</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.6990000009536743</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/online-tools-for-paralegals-automate-organize-and-streamline-with-legal-tech</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.6949999928474426</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-legal-tech-is-transforming-the-role-of-process-servers-and-service-of</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.6949999928474426</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.6940000057220459</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/streamline-process-serving-the-benefits-of-integrating-proof-into-clio-manage-for-legal-professionals</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.6940000057220459</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/server-policies</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0.7419999837875366</v>
+      <c r="D127" t="n">
+        <v>0.6930000185966492</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-paralegals-are-being-elevated-to-practice-certain-areas-of-law</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0.6919999718666077</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/10-top-apps-for-time-tracking-in-law-firms</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6880000233650208</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0.6869999766349792</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/success-stories</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/property-managers-streamline-service-of-process-with-process-server-provider</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0.6869999766349792</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/series-b</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.6859999895095825</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0.6850000023841858</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/on-the-job-tips-and-tricks-for-new-paralegals</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6790000200271606</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.6769999861717224</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/5-ways-that-proof-improves-productivity-for-litigation-lawyers</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.6769999861717224</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio-cloud-conference-gift-card</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-wins-clio-integration-award-for-best-practice-of-law-app</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6759999990463257</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/how-paralegals-can-help-their-firm-improve-operations</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6740000247955322</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/a-new-era-of-process-serving-in-florida-the-impact-of-hb-837-on-the-legal</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/join-proof-bing</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/compliance-and-jurisdictional/a-new-era-of-process-serving-in-florida-the-impact-of-hb-837-on-the-legal</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/server-policies</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/the-truth-about-process-servers</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.6690000295639038</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.6669999957084656</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-technology-and-filevine-announce-inventive-platform-integration-for-users-of-legal-case-management-software</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6669999957084656</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-wins-clio-integration-award-for-best-practice-of-law-app</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.6669999957084656</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/top-podcasts-for-paralegals</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.6660000085830688</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/holiday-gift-guide-for-paralegals</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.6629999876022339</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.6620000004768372</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/categories/paralegals</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/paralegal-productivity/tips-to-crush-your-goals-as-a-paralegal-and-grow-in-your-career</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.6579999923706055</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/associations/association-of-legal-administrators</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/time-management-tips-for-legal-administrators-and-paralegals</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.656000018119812</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/litify</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/integrate-proof-with-your-litify</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.6549999713897705</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/mycase</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.6549999713897705</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-best-practices/proof-s-new-chrome-extension-slashes-legal-document-processing-time-for-filevine-users</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.6529999971389771</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/integrations/clio</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.proofserve.com/learn/proof-technology-inc-closes-7m-series-a-funding</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.6499999761581421</v>
       </c>
     </row>
   </sheetData>
